--- a/后端/paletteseek_backend/数据.xlsx
+++ b/后端/paletteseek_backend/数据.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="artworks_final_100" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="artworks_final_100" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标签修正日志" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +774,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>棕色大地色系、黄色系、暖色调</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1055,12 +1056,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>蓝色系、橙色系、冷色调</t>
+          <t>冷感蓝色、蓝色系、红色点缀、冷暖平衡、中明度配色、柔和中饱和、强对比、蓝绿冷调、现代艺术感</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>清新、冷静、明快</t>
+          <t>理性、清爽、欢快、跳脱、现代、设计感</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1337,12 +1338,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>橙色系、黄色系、蓝绿色系、暖色调</t>
+          <t>暖色系、黄棕色点缀、青色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1619,12 +1620,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>棕色大地色系、黄色系、低饱和、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、低饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、克制、安静、温暖、典雅</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1901,12 +1902,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>棕色大地色系、橙色系、低明度、高饱和、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、高饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、活力、醒目、温暖、典雅</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2183,12 +2184,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>棕色大地色系、橙色系、暖色调</t>
+          <t>棕色调、棕色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2465,12 +2466,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>棕色大地色系、黄色系、暖色调</t>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2747,12 +2748,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>橙色系、红色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3029,12 +3030,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>黄色系、橙色系、棕色大地色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -3311,12 +3312,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、暖色调</t>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -3593,12 +3594,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>蓝色系、低明度、低饱和、冷色调</t>
+          <t>黑白深色、黑色系、冷色系、冷暖平衡、深色背景、低饱和、复古大地色、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>冷静、理性、稳重</t>
+          <t>沉稳、厚重、克制、安静、高级、怀旧</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -3875,12 +3876,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>红色系、紫色系、棕色大地色系、黄色系、绿色系</t>
+          <t>暖色系、紫色点缀、绿色点缀、温暖配色、中明度配色、柔和中饱和、强对比、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>热烈、活力、激情</t>
+          <t>温暖、欢快、跳脱、现代、设计感</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -4157,12 +4158,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>棕色大地色系、橙色系、蓝色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -4439,12 +4440,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>橙色系、黄色系、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -4721,12 +4722,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>橙色系、蓝色系、蓝绿色系、低饱和</t>
+          <t>黑白深色、黑色系、棕色点缀、冷暖平衡、深色背景、低饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>高级、克制、安静</t>
+          <t>沉稳、厚重、克制、安静、现代、设计感</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -5003,12 +5004,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>灰色系、低饱和</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、高级、现代、设计感</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -5285,12 +5286,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>蓝色系、橙色系、低饱和</t>
+          <t>高级灰、灰色系、蓝色点缀、冷感配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>冷静、理性、稳重</t>
+          <t>克制、安静、冷静、高级、现代、设计感</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -5567,12 +5568,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>棕色大地色系、低饱和</t>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>明亮、轻盈、克制、安静、温暖、现代</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -5849,12 +5850,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>棕色大地色系、低明度、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、柔和低对比、复古大地色</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -6131,12 +6132,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>橙色系、蓝色系、暖色调</t>
+          <t>高级灰、灰色系、棕色点缀、蓝色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -6413,12 +6414,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>蓝绿色系、冷色调</t>
+          <t>冷色系、蓝色点缀、冷感配色、中明度配色、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>清新、冷静、自然</t>
+          <t>冷静、自然、治愈、理性、清爽、现代</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -6695,12 +6696,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>棕色大地色系、橙色系、低饱和</t>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、低饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>克制、安静、温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -6977,12 +6978,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>黄色系、低饱和</t>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、低饱和、复古大地色、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>沉稳、厚重、克制、安静、温暖、高级</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -7259,12 +7260,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>黄色系、暖色调</t>
+          <t>黄棕色、黄棕色系、高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>温暖、欢快、跳脱、典雅、复古、含蓄</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -7541,12 +7542,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>灰色系、低饱和</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -7823,12 +7824,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>棕色大地色系、暖色调</t>
+          <t>暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、柔和低对比、现代艺术感</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -8105,12 +8106,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>棕色大地色系、橙色系、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -8387,12 +8388,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、低饱和</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -8669,12 +8670,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>棕色大地色系、低饱和</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -8951,12 +8952,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>黄色系、低饱和、暖色调</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -9233,12 +9234,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>橙色系、绿色系、黄色系、棕色大地色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、自然、治愈、现代、设计感</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -9515,12 +9516,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>黄色系、棕色大地色系、暖色调</t>
+          <t>棕色调、棕色系、黑白深色、黑色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -9797,12 +9798,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>黄色系、低饱和</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -10079,12 +10080,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>蓝绿色系、低饱和</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>清新、冷静、自然</t>
+          <t>克制、安静、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -10361,12 +10362,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>棕色大地色系、低饱和</t>
+          <t>高级灰、灰色系、蓝色点缀、冷暖平衡、中明度配色、低饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>克制、安静、现代、设计感</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -10643,12 +10644,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>红色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>热烈、活力、激情</t>
+          <t>温暖、典雅、复古、含蓄</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -10925,12 +10926,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>黄色系、蓝绿色系、低饱和</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>高级、克制、安静</t>
+          <t>克制、安静、高级、现代、设计感</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -11207,12 +11208,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -11489,12 +11490,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>蓝色系、棕色大地色系、冷色调</t>
+          <t>蓝色点缀、冷暖平衡、深色背景、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>科技、冷静、理性</t>
+          <t>沉稳、厚重、理性、清爽、现代、设计感</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -11771,12 +11772,12 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>黄色系、低饱和</t>
+          <t>高级灰、灰色系、棕色点缀、冷暖平衡、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>克制、安静、高级、现代、设计感</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -12053,12 +12054,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>黄色系、棕色大地色系、暖色调</t>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>高级、克制、安静</t>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -12335,12 +12336,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>橙色系、黄色系、暖色调</t>
+          <t>黄棕色、黄棕色系、黑白深色、黑色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>沉稳、厚重、温暖、欢快、跳脱、典雅</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -12617,12 +12618,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>橙色系、蓝绿色系、低明度、高饱和、冷色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、高饱和、复古大地色、极简黑白灰</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>沉稳、厚重、活力、醒目、温暖、高级</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -12899,12 +12900,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>棕色大地色系、黄色系、橙色系、绿色系、暖色调</t>
+          <t>棕色调、棕色系、黄棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>温暖、欢快、跳脱、典雅、复古</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -13181,12 +13182,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>橙色系、黄色系、棕色大地色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -13463,12 +13464,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>蓝色系、蓝绿色系、橙色系、冷色调</t>
+          <t>高级灰、灰色系、蓝色点缀、棕色点缀、冷感配色、中明度配色、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>冷静、理性、稳重</t>
+          <t>冷静、理性、清爽、欢快、跳脱、现代</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -13745,12 +13746,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>橙色系、蓝绿色系、棕色大地色系、暖色调</t>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -14027,12 +14028,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>棕色大地色系、橙色系、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -14309,12 +14310,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>橙色系、黄色系、棕色大地色系、暖色调</t>
+          <t>棕色调、棕色系、黄棕色、黄棕色系、温暖配色、中明度配色、高饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>活力、醒目、温暖、欢快、跳脱、典雅</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -14591,12 +14592,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>蓝色系、蓝绿色系、冷色调</t>
+          <t>冷感蓝色、蓝色系、青色点缀、冷感配色、中明度配色、柔和中饱和、蓝绿冷调、现代艺术感</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>清新、冷静、明快</t>
+          <t>冷静、理性、清爽、欢快、跳脱、现代</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -14873,12 +14874,12 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>蓝绿色系、低饱和、冷色调</t>
+          <t>高级灰、灰色系、冷感配色、中明度配色、低饱和、古典油画感</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>清新、冷静、自然</t>
+          <t>克制、安静、冷静、理性、清爽、典雅</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -15155,12 +15156,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>蓝绿色系、低饱和、冷色调</t>
+          <t>高级灰、灰色系、蓝色点缀、棕色点缀、冷感配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>清新、冷静、自然</t>
+          <t>克制、安静、冷静、理性、清爽、高级</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -15437,12 +15438,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>黄色系、蓝绿色系、橙色系、暖色调</t>
+          <t>米色浅色、米色系、棕色点缀、青色点缀、温暖配色、中明度配色、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>温暖、理性、清爽、欢快、跳脱、现代</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -15719,12 +15720,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>蓝绿色系、橙色系、低饱和、冷色调</t>
+          <t>高级灰、灰色系、米色浅色、米色系、冷暖平衡、中明度配色、低饱和、古典油画感</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>清新、冷静、自然</t>
+          <t>克制、安静、理性、清爽、典雅、复古</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -16001,12 +16002,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>黄色系、低饱和</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、黄棕色点缀、温暖配色、中明度配色、低饱和、极简黑白灰</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -16283,12 +16284,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>黄色系、绿色系、暖色调</t>
+          <t>自然绿色、绿色系、黄棕色点缀、棕色点缀、冷暖平衡、中明度配色、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>自然、治愈、欢快、跳脱、现代、设计感</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -16565,12 +16566,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>橙色系、暖色调</t>
+          <t>米色浅色、米色系、棕色点缀、温暖配色、明亮浅色、柔和中饱和、古典油画感</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>明亮、轻盈、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -16847,12 +16848,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>棕色大地色系、黄色系、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -17129,12 +17130,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>蓝色系、低饱和、冷色调</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>冷静、理性、稳重</t>
+          <t>克制、安静、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -17411,12 +17412,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>橙色系、低饱和</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -17693,12 +17694,12 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>棕色大地色系、橙色系、暖色调</t>
+          <t>棕色调、棕色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -17975,12 +17976,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>黄色系、低饱和</t>
+          <t>冷暖平衡、明亮浅色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>明亮、轻盈、克制、安静、高级、典雅</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -18257,12 +18258,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>橙色系、暖色调</t>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -18539,12 +18540,12 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>黄色系、棕色大地色系、低饱和</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、温暖配色、中明度配色、低饱和、复古大地色、极简黑白灰</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -18821,12 +18822,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>绿色系、黄色系、蓝绿色系、暖色调</t>
+          <t>棕色调、棕色系、黑白深色、黑色系、青色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>清新、自然、治愈</t>
+          <t>温暖、欢快、跳脱、典雅、复古</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -19103,12 +19104,12 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>蓝绿色系、蓝色系、绿色系、冷色调</t>
+          <t>冷色系、冷感配色、中明度配色、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>清新、冷静、自然</t>
+          <t>冷静、自然、治愈、理性、清爽、现代</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -19385,12 +19386,12 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>黄色系、低饱和</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -19667,12 +19668,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、暖色调</t>
+          <t>暖色系、黄棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -19949,12 +19950,12 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>黄色系、棕色大地色系、低饱和</t>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、低饱和、复古大地色、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>沉稳、厚重、克制、安静、温暖、高级</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -20231,12 +20232,12 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>黄色系</t>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、低饱和、极简黑白灰</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>克制、安静、温暖、高级</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -20513,12 +20514,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、黄色系、暖色调</t>
+          <t>暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -20795,12 +20796,12 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>橙色系、暖色调</t>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -21077,12 +21078,12 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>橙色系、红色系、棕色大地色系、暖色调</t>
+          <t>棕色调、棕色系、红色点缀、温暖配色、中明度配色、高饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>活力、醒目、温暖、欢快、跳脱、典雅</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -21359,12 +21360,12 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>橙色系、蓝绿色系、棕色大地色系、暖色调</t>
+          <t>暖色系、棕色点缀、蓝色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、理性、清爽、现代、设计感</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -21641,12 +21642,12 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>棕色大地色系、橙色系、暖色调</t>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -21923,12 +21924,12 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>黄色系、低饱和</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -22205,12 +22206,12 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>蓝绿色系、冷色调</t>
+          <t>冷色系、青色点缀、冷感配色、深色背景、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>清新、冷静、自然</t>
+          <t>沉稳、厚重、冷静、理性、清爽、现代</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -22487,12 +22488,12 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>黄色系、橙色系、蓝色系、蓝绿色系、暖色调</t>
+          <t>高级灰、灰色系、黄棕色点缀、棕色点缀、温暖配色、中明度配色、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -22769,12 +22770,12 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>黄色系、绿色系、暖色调</t>
+          <t>米色浅色、米色系、绿色点缀、冷暖平衡、中明度配色、柔和中饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>自然、治愈、现代、设计感</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -23051,12 +23052,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>橙色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、高饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>活力、醒目、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -23333,12 +23334,12 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>棕色大地色系、黄色系、橙色系、暖色调</t>
+          <t>暖色系、黄棕色点缀、绿色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -23615,12 +23616,12 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>棕色大地色系、低明度、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -23897,12 +23898,12 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>棕色大地色系、低饱和</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>克制、安静、高级</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -24179,12 +24180,12 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -24461,12 +24462,12 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>黄色系、暖色调</t>
+          <t>米色浅色、米色系、棕色调、棕色系、温暖配色、明亮浅色、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>明亮、轻盈、温暖、典雅、复古、含蓄</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -24743,12 +24744,12 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、低饱和</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -25025,12 +25026,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>黄色系、粉红色系、低饱和、暖色调</t>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、现代艺术感</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>明亮、轻盈、克制、安静、温暖、现代</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -25307,12 +25308,12 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>橙色系、低明度、低饱和</t>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、低饱和、复古大地色、极简黑白灰、东方传统色</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>沉稳、厚重、克制、安静、温暖、高级</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -25589,12 +25590,12 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>黄色系、橙色系、暖色调</t>
+          <t>棕色调、棕色系、高级灰、灰色系、温暖配色、中明度配色、柔和中饱和、复古大地色</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -25871,12 +25872,12 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>黄色系、棕色大地色系、暖色调</t>
+          <t>高级灰、灰色系、棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -26153,12 +26154,12 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>黄色系、低饱和</t>
+          <t>高级灰、灰色系、棕色点缀、冷暖平衡、明亮浅色、低饱和、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>明亮、轻盈、克制、安静、高级、现代</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -26435,12 +26436,12 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>灰色系、低饱和</t>
+          <t>高级灰、灰色系、冷暖平衡、明亮浅色、低饱和、强对比、极简黑白灰、现代艺术感</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>明亮、轻盈、克制、安静、高级、现代</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -26717,12 +26718,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>红色系、粉红色系、暖色调</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -26999,12 +27000,12 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、现代艺术感</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -27281,12 +27282,12 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>棕色大地色系、低饱和</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、东方传统色</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>克制、安静、高级、含蓄</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -27563,12 +27564,12 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>灰色系、低饱和</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、古典油画感</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、高级、典雅、复古、含蓄</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -27845,12 +27846,12 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>棕色大地色系、蓝色系、绿色系、暖色调</t>
+          <t>黑白深色、黑色系、暖色系、蓝色点缀、温暖配色、中明度配色、柔和中饱和、强对比、古典油画感</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -28127,12 +28128,12 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>黄色系、棕色大地色系、暖色调</t>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -28409,12 +28410,12 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>棕色大地色系、黄色系、暖色调</t>
+          <t>棕色调、棕色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>复古、沉稳、怀旧</t>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -28691,12 +28692,12 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>橙色系、棕色大地色系、低饱和、暖色调</t>
+          <t>暖色系、温暖配色、中明度配色、低饱和、复古大地色、古典油画感</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>活力、温暖、明朗</t>
+          <t>克制、安静、温暖、典雅、复古</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -28973,12 +28974,12 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>灰色系、低饱和</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、电影海报感</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>克制、安静、高级、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -29255,12 +29256,12 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>黄色系、棕色大地色系、暖色调</t>
+          <t>暖色系、黄棕色点缀、棕色点缀、温暖配色、明亮浅色、柔和中饱和、电影海报感</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>明亮、轻盈、温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -29537,12 +29538,12 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>绿色系、低明度</t>
+          <t>黑白深色、黑色系、冷色系、绿色点缀、冷感配色、深色背景、柔和中饱和、复古大地色、极简黑白灰</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>清新、自然、治愈</t>
+          <t>沉稳、厚重、冷静、自然、治愈、高级</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -29819,12 +29820,12 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>黄色系、暖色调</t>
+          <t>米色浅色、米色系、温暖配色、中明度配色、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>克制、安静、温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -30101,12 +30102,12 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>蓝绿色系、蓝色系、冷色调</t>
+          <t>黑白深色、黑色系、冷色系、蓝色点缀、冷感配色、深色背景、柔和中饱和、电影海报感</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>清新、冷静、自然</t>
+          <t>沉稳、厚重、冷静、理性、清爽、抓眼</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -30383,12 +30384,12 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>黑色系、低明度、低饱和</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、深色背景、低饱和、复古大地色、极简黑白灰</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>高级、克制、庄重</t>
+          <t>沉稳、厚重、克制、安静、高级、怀旧</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -30665,12 +30666,12 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>绿色系、蓝绿色系、低明度、冷色调</t>
+          <t>黑白深色、黑色系、冷色系、冷感配色、深色背景、柔和中饱和、复古大地色、极简黑白灰、电影海报感</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>清新、自然、治愈</t>
+          <t>沉稳、厚重、冷静、自然、治愈、高级</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -30947,12 +30948,12 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>红色系、棕色大地色系、橙色系、暖色调</t>
+          <t>暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>沉稳、典雅、复古</t>
+          <t>温暖、叙事、年代感</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -31229,12 +31230,12 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>黄色系、绿色系、暖色调</t>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、柔和中饱和、电影海报感</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>明亮、轻盈、温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -31511,12 +31512,12 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>黄色系、暖色调</t>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>明亮、温暖、精致</t>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -31793,12 +31794,12 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>蓝色系、冷色调、科技感、夜间感</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、电影海报感</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>科技、神秘、冷静</t>
+          <t>克制、安静、高级、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -32075,12 +32076,12 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>紫粉色系、梦幻色、浪漫感、霓虹感</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>浪漫、神秘、梦幻</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -32357,12 +32358,12 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>黄色金色系、明亮色、装饰感、轻奢感</t>
+          <t>暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>高级、温暖、精致</t>
+          <t>温暖、梦幻、浪漫、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -32639,12 +32640,12 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>黑白灰低饱和系、灰调、极简、高级感</t>
+          <t>黑白深色、黑色系、棕色点缀、青色点缀、冷暖平衡、深色背景、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>高级、庄重、克制</t>
+          <t>沉稳、厚重、欢快、跳脱、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -32921,12 +32922,12 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>绿色系、自然色、清新感、环保感</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>清新、自然、治愈</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -33203,12 +33204,12 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>棕色大地色系、复古色、怀旧感、历史感</t>
+          <t>米色浅色、米色系、黑白深色、黑色系、温暖配色、中明度配色、柔和中饱和、强对比、电影海报感</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>复古、庄重、怀旧</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -33485,12 +33486,12 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>多彩高对比系、海报感、高饱和、视觉冲击</t>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>活力、热烈、创意</t>
+          <t>沉稳、厚重、温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -33767,12 +33768,12 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>红橙色系、暖色调、高冲击、宣传感</t>
+          <t>高级灰、灰色系、鲜明红色、红色系、紫色点缀、冷暖平衡、中明度配色、柔和中饱和、电影海报感</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>活力、热烈、节日</t>
+          <t>欢快、跳脱、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -34049,12 +34050,12 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>蓝色系、冷色调、科技感、夜间感</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>科技、神秘、冷静</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -34331,12 +34332,12 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>紫粉色系、梦幻色、浪漫感、霓虹感</t>
+          <t>高级灰、灰色系、棕色点缀、红色点缀、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>浪漫、神秘、梦幻</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -34613,12 +34614,12 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>黄色金色系、明亮色、装饰感、轻奢感</t>
+          <t>黑白深色、黑色系、暖色系、温暖配色、中明度配色、柔和中饱和、强对比、电影海报感、视觉冲击</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>高级、温暖、精致</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -34895,12 +34896,12 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>黑白灰低饱和系、灰调、极简、高级感</t>
+          <t>高级灰、灰色系、蓝色点缀、冷暖平衡、中明度配色、柔和中饱和、极简黑白灰、电影海报感</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>高级、庄重、克制</t>
+          <t>高级、克制、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -35177,12 +35178,12 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>绿色系、自然色、清新感、环保感</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷感配色、中明度配色、柔和中饱和、强对比、极简黑白灰</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>清新、自然、治愈</t>
+          <t>冷静、高级、克制、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -35459,12 +35460,12 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>棕色大地色系、复古色、怀旧感、历史感</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、深色背景、柔和中饱和、复古大地色、极简黑白灰</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>复古、庄重、怀旧</t>
+          <t>沉稳、厚重、高级、克制、怀旧、抓眼</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -35741,12 +35742,12 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>多彩高对比系、海报感、高饱和、视觉冲击</t>
+          <t>冷感蓝色、蓝色系、绿色点缀、红色点缀、冷感配色、明亮浅色、柔和中饱和、蓝绿冷调、电影海报感</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>活力、热烈、创意</t>
+          <t>明亮、轻盈、冷静、理性、清爽、欢快</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -36023,12 +36024,12 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>红橙色系、暖色调、高冲击、宣传感</t>
+          <t>暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、强对比、复古大地色、电影海报感、视觉冲击</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>活力、热烈、节日</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -36305,12 +36306,12 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>蓝色系、冷色调、科技感、夜间感</t>
+          <t>米色浅色、米色系、棕色点缀、红色点缀、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>科技、神秘、冷静</t>
+          <t>温暖、梦幻、浪漫、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -36587,12 +36588,12 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>紫粉色系、梦幻色、浪漫感、霓虹感</t>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>浪漫、神秘、梦幻</t>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -36869,12 +36870,12 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>黄色金色系、明亮色、装饰感、轻奢感</t>
+          <t>暖色系、温暖配色、深色背景、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>高级、温暖、精致</t>
+          <t>沉稳、厚重、克制、安静、温暖、抓眼</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -37151,12 +37152,12 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>黑白灰低饱和系、灰调、极简、高级感</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、强对比、极简黑白灰、电影海报感、视觉冲击</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>高级、庄重、克制</t>
+          <t>克制、安静、高级、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -37433,12 +37434,12 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>绿色系、自然色、清新感、环保感</t>
+          <t>黄棕色点缀、棕色点缀、冷暖平衡、明亮浅色、柔和中饱和、电影海报感</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>清新、自然、治愈</t>
+          <t>明亮、轻盈、理性、清爽、欢快、跳脱</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -37715,12 +37716,12 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>棕色大地色系、复古色、怀旧感、历史感</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、电影海报感</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>复古、庄重、怀旧</t>
+          <t>克制、安静、高级、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -37997,12 +37998,12 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>多彩高对比系、海报感、高饱和、视觉冲击</t>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>活力、热烈、创意</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -38279,12 +38280,12 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>红橙色系、暖色调、高冲击、宣传感</t>
+          <t>暖色系、红色点缀、棕色点缀、温暖配色、中明度配色、柔和中饱和、强对比、电影海报感、视觉冲击</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>活力、热烈、节日</t>
+          <t>温暖、欢快、跳脱、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -38561,12 +38562,12 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>蓝色系、冷色调、科技感、夜间感</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、红色点缀、冷暖平衡、中明度配色、柔和中饱和、强对比</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>科技、神秘、冷静</t>
+          <t>高级、克制、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
@@ -38843,12 +38844,12 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>紫粉色系、梦幻色、浪漫感、霓虹感</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、电影海报感</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>浪漫、神秘、梦幻</t>
+          <t>克制、安静、高级、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -39125,12 +39126,12 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>黄色金色系、明亮色、装饰感、轻奢感</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、温暖配色、深色背景、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>高级、温暖、精致</t>
+          <t>沉稳、厚重、克制、安静、温暖、梦幻</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -39407,12 +39408,12 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>黑白灰低饱和系、灰调、极简、高级感</t>
+          <t>棕色调、棕色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>高级、庄重、克制</t>
+          <t>沉稳、厚重、温暖、高级、克制、抓眼</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -39689,12 +39690,12 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>绿色系、自然色、清新感、环保感</t>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>清新、自然、治愈</t>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -39971,12 +39972,12 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>棕色大地色系、复古色、怀旧感、历史感</t>
+          <t>暖色系、红色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>复古、庄重、怀旧</t>
+          <t>温暖、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -40253,12 +40254,12 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>多彩高对比系、海报感、高饱和、视觉冲击</t>
+          <t>黑白深色、黑色系、暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>活力、热烈、创意</t>
+          <t>温暖、梦幻、浪漫、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -40535,12 +40536,12 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>红橙色系、暖色调、高冲击、宣传感</t>
+          <t>冷色系、蓝色点缀、冷感配色、中明度配色、高饱和、电影海报感、视觉冲击、宣传招贴</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>活力、热烈、节日</t>
+          <t>活力、醒目、冷静、理性、清爽、梦幻</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -40817,12 +40818,12 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>蓝色系、冷色调、科技感、夜间感</t>
+          <t>黑白深色、黑色系、冷暖平衡、深色背景、低饱和、复古大地色、极简黑白灰、电影海报感</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>科技、神秘、冷静</t>
+          <t>沉稳、厚重、克制、安静、高级、怀旧</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -41099,12 +41100,12 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>紫粉色系、梦幻色、浪漫感、霓虹感</t>
+          <t>米色浅色、米色系、棕色点缀、温暖配色、明亮浅色、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>浪漫、神秘、梦幻</t>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -41381,12 +41382,12 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>黄色金色系、明亮色、装饰感、轻奢感</t>
+          <t>高级灰、灰色系、蓝色点缀、冷感配色、中明度配色、柔和中饱和、强对比、电影海报感、视觉冲击</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>高级、温暖、精致</t>
+          <t>冷静、理性、清爽、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -41663,12 +41664,12 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>黑白灰低饱和系、灰调、极简、高级感</t>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>高级、庄重、克制</t>
+          <t>克制、安静、温暖、高级、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -41945,12 +41946,12 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>绿色系、自然色、清新感、环保感</t>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、强对比、极简黑白灰、电影海报感、视觉冲击</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>清新、自然、治愈</t>
+          <t>克制、安静、高级、抓眼、宣传感</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -42227,12 +42228,12 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>棕色大地色系、复古色、怀旧感、历史感</t>
+          <t>高级灰、灰色系、冷感配色、中明度配色、低饱和、电影海报感</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>复古、庄重、怀旧</t>
+          <t>克制、安静、冷静、理性、清爽、抓眼</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -42509,12 +42510,12 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>多彩高对比系、海报感、高饱和、视觉冲击</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、深色背景、低饱和、复古大地色、极简黑白灰</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>活力、热烈、创意</t>
+          <t>沉稳、厚重、克制、安静、高级、抓眼</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -42791,12 +42792,12 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>红橙色系、暖色调、高冲击、宣传感</t>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、深色背景、低饱和、极简黑白灰、电影海报感</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>活力、热烈、节日</t>
+          <t>沉稳、厚重、克制、安静、高级、抓眼</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -43007,6 +43008,7222 @@
       <c r="BD151" t="inlineStr">
         <is>
           <t>白色</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L120"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>classification</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>style_tags</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>dominant_colors</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>color_ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>old_color_tags</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>new_color_tags</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>old_emotion_tags</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>new_emotion_tags</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>update_reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>869</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The Watermill with the Great Red Roof</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>巴洛克、古典艺术</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>#7E827B, #2C2315, #1B140C, #949184, #3B331E, #4B452E, #615A40, #77725F, #B2A791</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>17.29%, 16.49%, 16.28%, 14.52%, 11.77%, 7.68%, 5.82%, 5.76%, 4.37%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2189</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ready-to-Wear</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>现代艺术、当代艺术</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>#5084CA, #E5E2D9, #E24815, #2E2C31, #39373B, #445A7B, #B8B7BB, #907A81, #9B442F</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>29.33%, 19.08%, 17.96%, 17.00%, 13.06%, 1.16%, 0.93%, 0.81%, 0.68%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>冷感蓝色、蓝色系、红色点缀、冷暖平衡、中明度配色、柔和中饱和、强对比、蓝绿冷调、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>冷感蓝色、蓝色系、红色点缀、冷暖平衡、中明度配色、柔和中饱和、强对比、蓝绿冷调、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>理性、清爽、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>理性、清爽、欢快、跳脱、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2816</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Interior at Nice</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>野兽派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#AB8E78, #8A7767, #AFAA96, #A78046, #62564A, #8CA9AE, #588A97, #117773, #D0CDB8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>25.49%, 18.81%, 15.07%, 13.29%, 8.54%, 7.28%, 4.17%, 3.77%, 3.59%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、青色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>暖色系、黄棕色点缀、青色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4081</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gian Lodovico Madruzzo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>巴洛克、古典艺术</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>#181816, #6B6658, #5D574B, #7B7867, #534532, #8F6B4B, #342C23, #9C886E, #B7A387</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>47.73%, 12.94%, 10.08%, 6.98%, 6.23%, 5.42%, 4.96%, 3.64%, 2.01%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、低饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、低饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、温暖、怀旧</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、温暖、典雅</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4428</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mère Grégoire</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>写实主义、巴比松派、古典艺术</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>#352B17, #181104, #312008, #3E341F, #262111, #44230A, #55452E, #776045, #A59178</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>20.23%, 18.63%, 14.97%, 14.70%, 14.08%, 9.69%, 3.85%, 2.38%, 1.46%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、高饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、高饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、活力、醒目、温暖、热烈</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、活力、醒目、温暖、典雅</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4575</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Judith</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>巴洛克、古典艺术</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>#2C2925, #342F2A, #463629, #58412F, #B18362, #6C4E36, #BB9479, #9F7150, #865E41</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>29.82%, 22.83%, 11.98%, 8.98%, 6.54%, 6.42%, 4.61%, 4.53%, 4.28%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、橙色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4758</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Stoke-by-Nayland</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>新古典主义、浪漫主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>#3B3224, #504531, #241F17, #665940, #7F8B8F, #677378, #9CA7A9, #807152, #BEC8C7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>18.33%, 17.07%, 14.46%, 14.37%, 10.43%, 7.19%, 7.07%, 6.35%, 4.72%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4773</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Isabella Wolff</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>新古典主义、浪漫主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>#40201A, #532F20, #6D4529, #AF8F77, #997861, #81604A, #C6AB91, #261715, #DEC9AB</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>22.15%, 18.66%, 11.92%, 10.60%, 10.59%, 8.06%, 6.62%, 5.77%, 5.63%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4788</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lady Sarah Bunbury Sacrificing to the Graces</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>洛可可、古典艺术、装饰艺术</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>#614A28, #302119, #765D31, #4A3723, #B09888, #9A846D, #CFB6AD, #8E7347, #6C6557</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>18.16%, 15.02%, 14.34%, 12.84%, 9.89%, 9.29%, 8.37%, 7.34%, 4.74%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4796</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fishing Boats with Hucksters Bargaining for Fish</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>浪漫主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>#574F42, #726350, #A28C6F, #8B775D, #B7A080, #D1B690, #3A3020, #819097, #A0A6A2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>18.25%, 15.61%, 14.87%, 12.95%, 10.97%, 9.78%, 6.78%, 6.27%, 4.52%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4884</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Figure with Meat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Contemporary Art</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>现代艺术、当代艺术</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>#1C1E22, #28292E, #111519, #3B393B, #5A504C, #796F66, #233059, #9F9387, #CDC0B2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>34.98%, 21.64%, 17.96%, 9.25%, 5.84%, 3.94%, 2.76%, 2.63%, 1.01%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、冷暖平衡、深色背景、低饱和、复古大地色、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、冷色系、冷暖平衡、深色背景、低饱和、复古大地色、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、高级、怀旧</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、高级、怀旧</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5357</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The Red Armchair</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>立体主义、现代艺术、前卫艺术</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>#905FA5, #694346, #3E3432, #167A41, #F3EB69, #D09A40, #F1F3E8, #CE3830, #BFB2C6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20.94%, 19.30%, 19.13%, 15.71%, 8.61%, 8.00%, 3.95%, 2.68%, 1.68%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>暖色系、紫色点缀、绿色点缀、多彩拼色、温暖配色、中明度配色、柔和中饱和、强对比、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>暖色系、紫色点缀、绿色点缀、温暖配色、中明度配色、柔和中饱和、强对比、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>温暖、欢快、跳脱、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5848</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Landscape with Saint John on Patmos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>巴洛克、古典艺术</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>#3B301C, #262212, #513E28, #6A513D, #80A6C0, #7F6857, #BDC2BD, #7591A5, #A38874</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>21.53%, 20.88%, 17.13%, 11.44%, 8.38%, 7.18%, 4.61%, 4.60%, 4.25%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6565</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>American Gothic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>美国写实主义、地域主义、现代艺术</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>#1C1B19, #A6B7AB, #402A16, #B99C73, #7A5C38, #77705C, #A07E55, #504A3A, #CEBC99</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>29.28%, 15.77%, 12.16%, 9.04%, 7.82%, 7.63%, 6.49%, 6.38%, 5.42%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7021</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Portrait of Marevna</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>墨西哥壁画运动、现代艺术、社会现实主义</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>#212120, #353332, #687686, #395752, #6C4E3A, #A77455, #D9D8D3, #B7B4AF, #EAE77D</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>26.22%, 20.70%, 14.08%, 12.93%, 10.57%, 6.07%, 5.17%, 2.67%, 1.59%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、橙色点缀、冷暖平衡、深色背景、低饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、棕色点缀、冷暖平衡、深色背景、低饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8624</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Portrait of Pablo Picasso</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>#706562, #584F4F, #8A817E, #A39C99, #3C383C, #405B72, #B4B7B7, #8396A6, #5C7589</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>17.01%, 13.72%, 11.95%, 11.14%, 10.32%, 9.62%, 9.48%, 9.21%, 7.55%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、蓝色点缀、冷暖平衡、中明度配色、低饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、蓝色点缀、冷感配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>克制、安静、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>克制、安静、冷静、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8633</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hero Construction</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Contemporary Art</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>现代艺术、当代艺术</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>#FDF9F5, #F8F4F0, #F0EDEA, #3D3633, #584F4A, #221C1A, #7A716B, #9E9690, #BCB6B0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>32.23%, 29.38%, 24.70%, 4.72%, 2.59%, 2.46%, 1.44%, 1.36%, 1.11%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>冷暖平衡、明亮浅色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、高级、现代</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、现代</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8958</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Arrangement in Flesh Color and Brown: Portrait of Arthur Jerome Eddy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>#23211B, #27241D, #1D1C17, #2E2920, #342E23, #423829, #3B3326, #493D2D, #584836</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20.79%, 16.08%, 14.08%, 10.61%, 9.96%, 9.85%, 9.45%, 8.22%, 0.98%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、柔和低对比、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、柔和低对比、复古大地色</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8991</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Improvisation No. 30 (Cannons)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>抽象主义、现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>#AF9984, #8D7968, #7B9191, #B7ADA2, #6A4F45, #B7925B, #3C5A7C, #9F5347, #38444A</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>19.74%, 12.40%, 11.36%, 11.14%, 10.01%, 9.31%, 9.28%, 8.51%, 8.27%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、蓝色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、蓝色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>温暖、理性、清爽、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9503</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Champs de Mars: The Red Tower</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>#49443D, #2E2C28, #62615A, #E5DBCF, #C9C0AE, #7F7E76, #A3A298, #AF8761, #844934</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>16.01%, 14.64%, 12.93%, 10.48%, 9.84%, 9.78%, 9.57%, 8.65%, 8.09%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、橙色点缀、温暖配色、中明度配色、低饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、低饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>11272</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Maize and Cockscombs</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Asian Art</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>东方艺术、古典艺术、传统绘画</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>#B58A43, #A17839, #8B602F, #8A8A89, #62502A, #D7D6D3, #A4A5A3, #CDA052, #3C3221</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>23.62%, 19.81%, 11.04%, 10.51%, 9.25%, 8.12%, 7.51%, 7.15%, 2.98%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、温暖配色、中明度配色、柔和中饱和、复古大地色、红橙暖调、古典油画感</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>黄棕色、黄棕色系、高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古、含蓄</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>温暖、欢快、跳脱、典雅、复古、含蓄</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11393</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Henry Ossawa Tanner</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>#4A4B3B, #474535, #50503F, #423F31, #39342A, #785E43, #564131, #68513C, #7E775E</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>22.69%, 22.42%, 21.71%, 21.43%, 4.57%, 2.51%, 2.20%, 2.09%, 0.39%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、深色背景、柔和中饱和、柔和低对比、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、柔和低对比、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11434</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Salome with the Head of Saint John the Baptist</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>巴洛克、古典艺术</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>#312A21, #29241D, #3B3428, #5E4A3C, #494334, #553C26, #6D5948, #7E6B59, #95846C</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>23.30%, 19.81%, 19.63%, 8.26%, 8.20%, 6.84%, 6.14%, 4.65%, 3.17%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>11723</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Woman at Her Toilette</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>写实主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>#A49D96, #928E89, #B3AEA8, #7E7E7C, #746B5F, #5F5847, #44402C, #937D67, #CAC3BC</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>18.21%, 17.02%, 14.06%, 13.11%, 12.35%, 9.70%, 5.32%, 5.23%, 5.00%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>13720</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Alabama Cotton Tenant Farmer's Wife</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>纪实摄影、现代艺术</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>#A9A79B, #98968A, #888579, #767367, #605E52, #BBBAAE, #49483C, #13140C, #2D2D22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>15.45%, 14.65%, 14.28%, 11.64%, 11.31%, 9.43%, 8.43%, 7.46%, 7.35%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>13853</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Karttikeya, Commander of the Divine Army, Seated on a Peacock</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Asian Art</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>东方艺术、古典艺术、传统绘画</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>#E9E8E6, #ADABA1, #DBDAD8, #9B9783, #837F6C, #C3C1B8, #6A6550, #4E4834, #2E2A1D</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20.79%, 14.17%, 13.12%, 11.33%, 10.45%, 9.95%, 8.88%, 6.31%, 4.99%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>14572</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The Millinery Shop</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>#5C3F28, #774924, #37423C, #403022, #6D693D, #945921, #798867, #A37B48, #C1A47A</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>21.69%, 14.39%, 13.94%, 12.96%, 12.69%, 9.26%, 6.80%, 4.99%, 3.28%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>温暖、自然、治愈、热烈、怀旧、现代</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>温暖、自然、治愈、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>14574</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Henri Degas and His Niece Lucie Degas (The Artist's Uncle and Cousin)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>写实主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>#2C261E, #14130E, #483928, #65533B, #7E6D50, #9A8961, #C2A265, #E2D089, #B0AD8A</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>19.84%, 18.71%, 14.28%, 10.55%, 9.31%, 8.97%, 7.87%, 6.98%, 3.51%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、黑白深色、黑色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14968</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Mural Fragment Depicting a Maguey Bloodletting Ritual</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>古典艺术、传统绘画</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>#81392D, #762618, #A86153, #924D41, #B97769, #C8C6C6, #C0998D, #453F3B, #79706A</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>19.18%, 17.62%, 17.59%, 16.20%, 11.67%, 9.38%, 4.44%, 2.11%, 1.81%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>鲜明红色、红色系、温暖配色、中明度配色、柔和中饱和、红橙暖调、古典油画感</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古、含蓄</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古、含蓄</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>15468</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Saint George and the Dragon</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>文艺复兴、古典艺术、宗教艺术</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>#AD875D, #B99E81, #C8B69F, #2B1B08, #4F3813, #9A6E39, #7C531C, #847A6E, #5A5441</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>18.11%, 13.56%, 12.71%, 12.22%, 11.94%, 10.88%, 9.49%, 6.79%, 4.31%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>16146</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Equestrienne (At the Cirque Fernando)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>#CCC3B9, #BEB6A7, #A9A195, #938D85, #7E7B76, #6B6966, #555656, #824D44, #8E765A</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>23.06%, 15.60%, 11.66%, 10.98%, 9.96%, 8.60%, 8.42%, 7.74%, 3.99%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、冷暖平衡、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>克制、安静、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>16169</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>The Beheading of Saint John the Baptist</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>文艺复兴、古典艺术、宗教艺术</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>#B1A892, #9D9484, #6B6654, #4F4D44, #372F29, #87826F, #855834, #A67D52, #6B8297</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>29.96%, 21.94%, 10.22%, 9.41%, 8.34%, 8.26%, 5.10%, 4.32%, 2.44%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、中明度配色、低饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>16231</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Processional Cross with Saint Mary Magdalene and a Blessed Hermit</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>文艺复兴、古典艺术、宗教艺术</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>#030302, #AD7E3E, #4D3621, #C39653, #96652E, #665D4A, #9C2D16, #DBC49D, #998C73</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>46.86%, 17.24%, 7.59%, 7.48%, 7.30%, 4.29%, 4.22%, 2.72%, 2.31%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、红橙暖调</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>黄棕色、黄棕色系、黑白深色、黑色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、热烈、怀旧、典雅</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、欢快、跳脱、典雅</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>16298</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Portrait of Jean Gros (recto); Coat of Arms of Jean Gros (verso)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>文艺复兴、古典艺术、宗教艺术</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>#120A05, #081114, #051A22, #1C130C, #8A6453, #7A5645, #614333, #402C21, #9A7566</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>29.39%, 20.31%, 14.96%, 14.21%, 6.44%, 5.69%, 3.86%, 3.27%, 1.88%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、高饱和、复古大地色、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、高饱和、复古大地色、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、活力、醒目、温暖、高级</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、活力、醒目、温暖、高级</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>16327</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>The Annunciation</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>文艺复兴、古典艺术、宗教艺术</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>#4D3D2A, #372518, #783927, #64644A, #987331, #8E9079, #203643, #27560A, #C8C3B6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>21.41%, 17.84%, 15.13%, 13.11%, 9.94%, 8.65%, 6.29%, 4.75%, 2.88%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、黄棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>温暖、欢快、跳脱、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>16362</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Friar Pedro Shoots El Maragato as His Horse Runs Off</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>新古典主义、浪漫主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>#4E3A1E, #5D482C, #948464, #231B0E, #79582A, #392B17, #857455, #AA9672, #6B5C40</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>16.70%, 12.11%, 11.84%, 11.44%, 11.41%, 11.04%, 9.61%, 7.99%, 7.86%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>16487</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>The Bay of Marseille, Seen from L'Estaque</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>后印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>#809BA1, #44687C, #587788, #98A8A8, #6C7262, #9C7C5E, #80897D, #4A615A, #BA9771</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>17.57%, 15.99%, 12.99%, 12.91%, 10.85%, 9.29%, 7.31%, 6.99%, 6.10%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>冷色系、蓝色点缀、冷感配色、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、蓝色点缀、棕色点缀、冷感配色、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>冷静、理性、清爽、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>冷静、理性、清爽、欢快、跳脱、现代</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>16488</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Armida Encounters the Sleeping Rinaldo</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>洛可可、古典艺术、装饰艺术</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>#ACBFC4, #524134, #D3BCA2, #7A5F4A, #927F6A, #AD9C87, #2F231C, #DB9769, #A63C2A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>26.31%, 13.29%, 11.36%, 11.23%, 11.06%, 10.61%, 9.27%, 4.56%, 2.33%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>16499</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Jesus Mocked by the Soldiers</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>写实主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>#060809, #3B342C, #21201D, #524A41, #CDB392, #92775B, #765A42, #AD947C, #D7CFB7</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>35.97%, 11.72%, 10.44%, 9.87%, 7.39%, 6.76%, 6.69%, 6.12%, 5.05%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>16551</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Beata Beatrix</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>写实主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>#362715, #B99350, #C0C0C0, #4F361A, #6E4820, #A37D40, #866132, #DCB560, #918D88</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>17.48%, 14.95%, 14.29%, 13.89%, 12.31%, 11.23%, 10.89%, 2.82%, 2.14%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、温暖配色、中明度配色、高饱和、复古大地色、红橙暖调、古典油画感</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、黄棕色、黄棕色系、温暖配色、中明度配色、高饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>活力、醒目、温暖、热烈、怀旧、典雅</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>活力、醒目、温暖、欢快、跳脱、典雅</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>16568</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Water Lilies</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>#506775, #59819F, #365F71, #436F8E, #607680, #4C6F5B, #265653, #7E908E, #A2A7A4</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>17.14%, 15.03%, 14.81%, 13.69%, 13.30%, 8.61%, 7.40%, 6.69%, 3.34%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>冷感蓝色、蓝色系、青色点缀、冷感配色、中明度配色、柔和中饱和、蓝绿冷调、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>冷感蓝色、蓝色系、青色点缀、冷感配色、中明度配色、柔和中饱和、蓝绿冷调、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>冷静、理性、清爽、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>冷静、理性、清爽、欢快、跳脱、现代</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>16571</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Arrival of the Normandy Train, Gare Saint-Lazare</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>写实主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>#4B5E5B, #3A494C, #738281, #A9AFB1, #647064, #889699, #293338, #566C79, #C3C8C8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>17.27%, 14.97%, 12.94%, 11.63%, 11.47%, 10.20%, 10.19%, 8.54%, 2.77%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、冷色系、冷感配色、中明度配色、低饱和、古典油画感</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、冷感配色、中明度配色、低饱和、古典油画感</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>克制、安静、冷静、理性、清爽、典雅</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>克制、安静、冷静、理性、清爽、典雅</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>16776</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>After the Hurricane, Bahamas</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Print / Drawing</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>版画、平面设计、古典艺术</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>#D5D1C6, #8B9291, #36525E, #5E7276, #363231, #8BB6C1, #F0E6D9, #BAB5AA, #815E4C</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>17.74%, 13.54%, 12.68%, 10.86%, 10.38%, 10.38%, 9.39%, 8.59%, 6.44%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、冷色系、蓝色点缀、冷感配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、蓝色点缀、棕色点缀、冷感配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>克制、安静、冷静、理性、清爽、高级</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>克制、安静、冷静、理性、清爽、高级</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>16964</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>The Plough and the Song</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Contemporary Art</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>现代艺术、当代艺术</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>#D1CCA7, #BBB498, #557C86, #9A562E, #79939A, #356FB0, #E0DACB, #AA7D5B, #403537</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>22.97%, 17.32%, 12.87%, 12.84%, 9.21%, 8.54%, 7.33%, 6.67%, 2.25%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>暖色系、青色点缀、橙色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、棕色点缀、青色点缀、温暖配色、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>温暖、理性、清爽、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>温暖、理性、清爽、欢快、跳脱、现代</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>18709</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>The Frugal Meal, from The Saltimbanques</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Print / Drawing</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>版画、平面设计、古典艺术</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>#F2DECA, #354545, #445554, #AAB0A3, #556763, #949F95, #C3C2B3, #7D8C85, #687873</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>34.61%, 12.44%, 10.05%, 8.17%, 7.59%, 7.37%, 6.91%, 6.44%, 6.42%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、冷暖平衡、中明度配色、低饱和、古典油画感</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、米色浅色、米色系、冷暖平衡、中明度配色、低饱和、古典油画感</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>克制、安静、理性、清爽、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>克制、安静、理性、清爽、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>18757</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ceremonial Knife (Tumi)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>文艺复兴、古典艺术、宗教艺术</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>#474646, #333333, #C4A357, #626160, #AC8A43, #CFB271, #8C6E35, #E0CEB1, #67A0A6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>34.41%, 25.82%, 12.08%, 9.22%, 6.74%, 5.29%, 4.91%, 1.04%, 0.49%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、高级灰、灰色系、黑白深色、黑色系、温暖配色、中明度配色、低饱和</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、黄棕色点缀、温暖配色、中明度配色、低饱和、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>19339</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Arlésiennes (Mistral)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>后印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>#485B31, #BAAB93, #A37321, #1A2C3B, #686A3A, #989266, #316A4D, #9C3D27, #69767B</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>16.82%, 12.82%, 12.46%, 11.96%, 11.41%, 9.51%, 8.91%, 8.52%, 7.59%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>自然绿色、绿色系、橙色点缀、红色点缀、冷暖平衡、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>自然绿色、绿色系、黄棕色点缀、棕色点缀、冷暖平衡、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>自然、治愈、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>自然、治愈、欢快、跳脱、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>20432</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>The Old Savoyard</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Print / Drawing</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>版画、平面设计、古典艺术</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>#D6B99E, #D0AE93, #C89E85, #BB8E77, #916558, #AE7865, #958072, #9F9E9D, #6F5047</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>27.78%, 17.06%, 14.69%, 11.39%, 7.78%, 7.27%, 5.06%, 4.65%, 4.33%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、明亮浅色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、棕色点缀、温暖配色、明亮浅色、柔和中饱和、古典油画感</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>20579</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Hercules and the Lernaean Hydra</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>写实主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>#251D10, #312516, #3E3120, #4B3F2C, #5C513B, #8A785A, #71634B, #9B8C6E, #AEA180</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>24.06%, 22.64%, 13.56%, 10.00%, 7.04%, 6.74%, 6.18%, 5.24%, 4.54%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、热烈、怀旧、典雅</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>21023</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Buddha Shakyamuni Seated in Meditation (Dhyanamudra)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Asian Art</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>东方艺术、古典艺术、传统绘画</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>#545250, #625E5B, #6F6F6F, #7F6E61, #504238, #D5D5D5, #958478, #352B24, #B3B1AF</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>26.49%, 22.49%, 15.03%, 9.37%, 8.34%, 7.09%, 6.36%, 3.61%, 1.21%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>23333</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Pastoral Scene</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>洛可可、古典艺术、装饰艺术</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>#281E16, #36261B, #4A311F, #60402B, #765A43, #8E745B, #AB8C72, #ECD3B5, #CEAA8C</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>30.70%, 28.00%, 15.73%, 7.27%, 5.37%, 4.74%, 3.72%, 2.39%, 2.07%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、热烈、怀旧、典雅</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>23684</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>The Artist's Mother</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Print / Drawing</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>版画、平面设计、古典艺术</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>#6C5E51, #78695A, #A18D77, #867563, #94826E, #5E5248, #B29A7F, #FAEBD5, #DCC6AB</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>19.11%, 16.25%, 15.23%, 14.46%, 14.10%, 9.89%, 5.97%, 4.24%, 0.76%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>23700</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>The Praying Jew</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>#242423, #D9D9CB, #37342F, #C3C1B6, #AFAD9F, #6F695B, #9A9684, #88806D, #564E43</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>45.56%, 9.88%, 8.20%, 8.12%, 6.30%, 5.93%, 5.57%, 5.41%, 5.04%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、中明度配色、低饱和、复古大地色、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、温暖配色、中明度配色、低饱和、复古大地色、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、怀旧、现代</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>23972</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Virgin and Child with the Young Saint John the Baptist</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>文艺复兴、古典艺术、宗教艺术</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>#212718, #564122, #320B0A, #836C45, #BDB3AB, #849FA6, #A78E6F, #2F616A, #A73C29</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>29.33%, 14.51%, 11.26%, 10.69%, 8.57%, 7.42%, 7.14%, 6.49%, 4.58%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、青色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、黑白深色、黑色系、青色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>温暖、欢快、跳脱、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>24548</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Shiva as Lord of the Dance (Nataraja)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Asian Art</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>东方艺术、古典艺术、传统绘画</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>#B0B0AE, #BCBBBA, #A09E9B, #8D8D8C, #746D4D, #565135, #CCCCCB, #928968, #35311D</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20.16%, 19.04%, 15.57%, 15.20%, 7.01%, 7.00%, 6.94%, 5.10%, 3.97%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>24836</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Brushstroke with Spatter</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Contemporary Art</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>波普艺术、现代艺术</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>#BB998F, #C6A69C, #AE8A80, #2E2A27, #9D786F, #E3D308, #2C2D76, #5E5132, #A09516</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>24.24%, 20.53%, 16.20%, 14.91%, 9.06%, 5.81%, 4.33%, 3.18%, 1.74%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>暖色系、黄色点缀、温暖配色、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>暖色系、黄棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25853</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wine Cistern</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Applied Art</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>装饰艺术、工艺美术、应用设计</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>#919392, #A9A9A8, #C2C1BD, #A19152, #6A6F69, #906C20, #CBB775, #464020, #DCAA23</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>24.82%, 21.99%, 12.33%, 9.02%, 8.28%, 6.88%, 5.89%, 5.86%, 4.94%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、橙色点缀、黄色点缀、温暖配色、中明度配色、低饱和、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、低饱和、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>25865</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>The Herring Net</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>#7F6A50, #745F46, #292216, #545142, #3B4136, #3F301C, #646355, #7B7A69, #949078</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>26.09%, 19.49%, 10.74%, 9.44%, 8.91%, 7.86%, 7.80%, 7.09%, 2.59%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>27307</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Madame de Pastoret and Her Son</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>新古典主义、浪漫主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>#A0907C, #94826D, #D7D6C2, #C6BFAB, #836F59, #B1A18C, #77512D, #573517, #9F6830</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>23.68%, 21.89%, 13.86%, 10.24%, 8.21%, 7.92%, 6.34%, 3.99%, 3.87%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>27310</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>The Holy Family with Saints Elizabeth and John the Baptist</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>巴洛克、古典艺术</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>#3E271B, #1C1410, #704425, #AE281A, #3F484A, #996D4E, #C29875, #E4C29E, #761911</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>18.28%, 17.39%, 15.55%, 14.44%, 8.93%, 7.97%, 6.28%, 5.74%, 5.42%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>暖色系、红色点缀、橙色点缀、温暖配色、中明度配色、高饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、红色点缀、温暖配色、中明度配色、高饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>活力、醒目、温暖、热烈、怀旧、典雅</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>活力、醒目、温暖、欢快、跳脱、典雅</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>27984</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Woman before an Aquarium</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>野兽派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>#896C54, #5B707A, #41261D, #4E4033, #695643, #9C8470, #345969, #779290, #B1B5A4</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>16.47%, 15.59%, 13.72%, 13.04%, 12.53%, 9.01%, 8.68%, 6.54%, 4.43%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>暖色系、蓝色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>暖色系、棕色点缀、蓝色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>温暖、理性、清爽、热烈、怀旧、现代</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>温暖、理性、清爽、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>27987</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Jacques and Berthe Lipchitz</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>#372520, #292525, #3A3D3C, #646860, #543A2A, #4E524F, #A6674A, #7F523C, #858376</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>30.76%, 13.47%, 12.41%, 12.28%, 7.98%, 7.77%, 6.75%, 6.41%, 2.16%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、深色背景、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>27992</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A Sunday on La Grande Jatte — 1884</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>后印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>#525D56, #464E4A, #615F67, #A19A6D, #747477, #736E5A, #8F8167, #8D9499, #B3AB9F</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>19.09%, 14.72%, 13.22%, 11.21%, 11.08%, 9.92%, 9.52%, 7.23%, 4.01%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>28560</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>The Bedroom</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>后印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>#7A94B0, #768E87, #9A8F83, #A57811, #857C69, #8F652E, #4C5C53, #BBB891, #A09646</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>17.97%, 15.99%, 15.91%, 15.68%, 13.87%, 6.35%, 5.81%, 4.25%, 4.17%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黄棕色点缀、棕色点缀、温暖配色、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>温暖、自然、治愈、热烈、怀旧、现代</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>28849</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>A City Park</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>#CFB992, #D1C1A4, #DAD9D4, #91AC56, #5E7349, #7B8B59, #455939, #A2A379, #2A3624</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20.53%, 18.44%, 12.35%, 11.23%, 9.03%, 8.93%, 8.28%, 7.04%, 4.17%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>绿色点缀、冷暖平衡、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、绿色点缀、冷暖平衡、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>自然、治愈、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>自然、治愈、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>30709</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bar-room Scene</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>新古典主义、浪漫主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>#775936, #6C4F32, #63462D, #83633E, #937145, #A17B4D, #4E3826, #36281F, #C1956F</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20.58%, 20.11%, 15.64%, 11.28%, 10.56%, 8.85%, 6.54%, 5.53%, 0.93%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、温暖配色、中明度配色、高饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、高饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>活力、醒目、温暖、热烈、怀旧、典雅</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>活力、醒目、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>30839</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>The Philosopher's Conquest</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>#4A4234, #353129, #827D65, #625C47, #D6CBB8, #A47C44, #3C7A51, #7D4C37, #A99F84</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>29.67%, 16.26%, 12.49%, 10.53%, 9.06%, 7.87%, 6.32%, 5.34%, 2.47%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、绿色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>暖色系、黄棕色点缀、绿色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>31285</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Portrait of Mary Adeline Williams</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>印象派、现代艺术</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>#261F18, #332319, #171815, #323027, #4E3F32, #A98769, #C2A68A, #DCC6B1, #866146</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>30.33%, 25.12%, 20.50%, 13.31%, 4.18%, 1.83%, 1.82%, 1.69%, 1.22%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>34181</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>La durée poignardée (Time Transfixed)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>#75573C, #89745E, #574D43, #655C52, #393431, #45403A, #AFA394, #87633D, #A29785</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>17.46%, 15.84%, 13.71%, 12.95%, 10.85%, 9.44%, 9.39%, 5.94%, 4.42%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>34286</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Mirror Frame with Tree of Life Motif</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Asian Art</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>东方艺术、古典艺术、传统绘画</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>#F5F5F5, #D2CCB6, #C3BCA0, #8D794E, #B2A583, #9A8C68, #6E5742, #B89158, #722629</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>21.23%, 17.81%, 15.51%, 12.11%, 11.31%, 11.19%, 4.92%, 3.88%, 2.04%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、明亮浅色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、棕色调、棕色系、温暖配色、明亮浅色、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、温暖、典雅、复古、含蓄</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>34299</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Landscapes</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Asian Art</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>东方艺术、古典艺术、传统绘画</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>#EADFD4, #807770, #6E665F, #938981, #5D554F, #A79D93, #BCB3A7, #4A443F, #D4C8BD</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>29.32%, 11.52%, 11.17%, 10.18%, 10.04%, 8.33%, 7.77%, 6.35%, 5.31%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、低饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、极简黑白灰、古典油画感</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、典雅、复古、含蓄</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>35198</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Miss E. Knows</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Contemporary Art</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>现代艺术、当代艺术</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>#EAE1C4, #DAD1B5, #CC9EB8, #96998E, #46454D, #6D6487, #AA5B07, #997B52, #D7C70F</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>33.96%, 20.76%, 14.74%, 13.74%, 7.73%, 3.09%, 2.68%, 2.65%, 0.65%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、明亮浅色、低饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、怀旧</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、现代</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>36132</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cope</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Textiles</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>装饰艺术、工艺美术、应用设计</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>#4E4E4E, #543317, #6B451E, #3B2410, #B09256, #815C28, #9C7D45, #766C4D, #C1A878</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>33.14%, 14.68%, 12.41%, 11.97%, 9.39%, 7.32%, 6.66%, 2.54%, 1.89%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、高级灰、灰色系、温暖配色、中明度配色、柔和中饱和、复古大地色</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、高级灰、灰色系、温暖配色、中明度配色、柔和中饱和、复古大地色</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>温暖</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>36161</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tall Clock</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>#BEB9AE, #4F2F28, #32201A, #C7C5BE, #ABA396, #847969, #736657, #73453B, #999082</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>18.71%, 15.01%, 12.54%, 10.70%, 10.11%, 9.91%, 7.71%, 7.69%, 7.61%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>37368</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Spanish Dancer</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Modern Art</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>#D1D4C5, #C6C9B8, #DCE0D3, #BBBDAA, #B0AD97, #886F51, #B19A6A, #969485, #4D4438</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20.58%, 20.04%, 17.74%, 16.23%, 9.80%, 4.73%, 4.48%, 3.80%, 2.59%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、暖色系、温暖配色、明亮浅色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、冷暖平衡、明亮浅色、低饱和、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、高级</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、高级、现代</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>37761</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Spoon Woman</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Contemporary Art</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>现代艺术、表现主义</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>#E9E9E9, #E0E0E0, #CFCFCF, #2F3130, #404241, #C0C0C0, #1B1C1B, #535555, #7F817F</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>39.61%, 26.12%, 9.91%, 6.66%, 6.18%, 5.61%, 3.55%, 1.93%, 0.43%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>冷暖平衡、明亮浅色、低饱和、强对比、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、冷暖平衡、明亮浅色、低饱和、强对比、极简黑白灰、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、高级、现代</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、高级、现代</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>38930</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Two Plant Specimens</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Photography</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>纪实摄影、现代艺术</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>#9B6D6C, #936461, #B7A1AC, #A37778, #895C58, #B2949B, #AB8588, #7D554F, #D0BDA0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>17.99%, 15.34%, 14.26%, 12.34%, 12.14%, 9.13%, 8.73%, 8.67%, 1.41%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>40619</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Zapata</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>墨西哥壁画运动、现代艺术、社会现实主义</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>#1C1714, #2B201A, #46261B, #5E2D1E, #594E43, #726051, #473A31, #79442B, #8F7D6A</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>25.90%, 20.59%, 13.24%, 12.44%, 7.59%, 6.59%, 5.34%, 5.18%, 3.13%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、现代艺术感</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、热烈、怀旧、现代</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、现代、设计感</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>43145</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>View of Delphi with a Procession</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>巴洛克、古典艺术</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>#262820, #353628, #494632, #A3B4D0, #98A2B2, #7F98CC, #645E45, #C6CDDE, #7C7E74</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>24.34%, 23.32%, 11.87%, 11.17%, 7.20%, 6.79%, 6.13%, 5.94%, 3.24%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、蓝色点缀、冷暖平衡、中明度配色、柔和中饱和、强对比、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、蓝色点缀、温暖配色、中明度配色、柔和中饱和、强对比、古典油画感</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>43714</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>E-10: English Dining Room of the Georgian Period, 1770-90</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Applied Art</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>装饰艺术、工艺美术、应用设计</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>#7B7A5D, #6D6440, #92927B, #53492B, #39260B, #ADAB98, #1C070B, #B08C4A, #E4D5C9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>22.99%, 16.45%, 13.65%, 13.49%, 10.17%, 10.10%, 7.59%, 3.23%, 2.33%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、温暖配色、中明度配色、柔和中饱和</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>温暖、怀旧</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>温暖</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>44018</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Croquet Scene</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>American Art</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>写实主义、古典艺术</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>#382D20, #473A24, #59492C, #364A49, #8B856E, #8A3928, #45686A, #6C634E, #ADAC96</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>28.74%, 28.59%, 23.33%, 3.93%, 3.66%, 3.17%, 3.15%, 3.14%, 2.29%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、深色背景、柔和中饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、热烈、怀旧、典雅</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>44741</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>The Annunciation</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Painting / Sculpture</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>巴洛克、古典艺术</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>#EFEFEC, #776556, #67564B, #877462, #E1E3E0, #55463C, #978576, #3E312A, #AB9A8C</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>18.03%, 14.23%, 12.73%, 12.20%, 11.73%, 10.50%, 9.40%, 6.18%, 5.00%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、低饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、低饱和、复古大地色、古典油画感</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、怀旧、典雅、复古</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、典雅、复古</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>900002</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>"Paulchens Millionenkuss"</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>#ECCC87, #F5D89A, #393A2C, #E6C176, #C6A553, #D6B364, #504E3A, #807041, #A78A4A</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>29.30%, 16.73%, 12.31%, 11.16%, 10.15%, 9.03%, 4.91%, 3.30%, 3.12%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、温暖配色、明亮浅色、柔和中饱和、复古大地色、红橙暖调、电影海报感</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>暖色系、黄棕色点缀、棕色点缀、温暖配色、明亮浅色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、温暖、热烈、怀旧、抓眼</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>900003</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>"Projekt Marmor – verdrängt und vergessen" offizielles Filmposter (deutsch)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>#0C0F0B, #212C19, #E1E1E1, #385A25, #414141, #666665, #5C8336, #8F9684, #BBBDB7</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>47.78%, 16.34%, 8.01%, 7.71%, 5.58%, 4.46%, 3.88%, 3.31%, 2.92%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、冷色系、绿色点缀、冷感配色、深色背景、柔和中饱和、极简黑白灰、电影海报感</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、冷色系、绿色点缀、冷感配色、深色背景、柔和中饱和、复古大地色、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、冷静、自然、治愈、高级</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、冷静、自然、治愈、高级</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>900004</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>"האיש הנעלם - הסיפור של וילפריד ישראל" - פוסטר</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>#CEC3A3, #DBD3B6, #BEB191, #877F6E, #A19987, #3D3A34, #B5A171, #656056, #070606</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>22.18%, 19.96%, 17.93%, 9.90%, 8.92%, 7.06%, 6.32%, 6.30%, 1.44%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、低饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、温暖配色、中明度配色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>900008</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1935 Sri Krishna Leelalu poster</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>#594D52, #6B5357, #7F5657, #9A5E59, #816C6D, #BC8D7F, #A17A73, #D6A28C, #C16657</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>23.02%, 21.34%, 13.91%, 8.42%, 7.98%, 7.59%, 7.22%, 5.36%, 5.17%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>温暖、叙事、年代感</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>温暖、叙事、年代感</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>900009</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1940, Fredric March as Jean Lafitte on original program for movie The Buccaneer</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>#EADBAA, #DED1A1, #CAC298, #B9B58D, #929474, #A3A381, #7A7F62, #5D664E, #3E4D39</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>21.84%, 16.61%, 14.46%, 12.12%, 10.96%, 10.81%, 5.91%, 4.45%, 2.83%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、明亮浅色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、温暖、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>900010</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1960 Maharathi Karna poster</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>#FDEDC4, #DDCAA8, #C8B99B, #B1A58C, #F4DCB7, #99907C, #7F7B6A, #636357, #43463F</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20.25%, 15.61%, 12.07%, 10.49%, 10.18%, 10.07%, 9.79%, 7.47%, 4.08%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、明亮浅色、低饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、怀旧</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>900012</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2100x1400 CTH Poster Art</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>#716443, #817556, #A19B84, #5D5135, #938B6E, #45392A, #B3AFA2, #2B2518, #E1E0DD</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>17.68%, 16.27%, 15.31%, 13.66%, 13.47%, 10.65%, 5.99%, 5.86%, 1.11%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>900013</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>54 first years - Avi Mograbi - poster</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>#493D48, #2C2835, #12131F, #685860, #938486, #D2B492, #A0605B, #C78C5D, #E7DFCF</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>21.02%, 20.71%, 15.77%, 12.72%, 8.70%, 7.00%, 6.44%, 5.34%, 2.31%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>温暖、梦幻、浪漫、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>温暖、梦幻、浪漫、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>900014</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>@Followers poster 2025</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>#262623, #110E0C, #563C2F, #936747, #CBA46D, #285457, #588F8A, #8CCCBB, #EAE0C0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>24.77%, 24.46%, 12.77%, 9.21%, 7.56%, 6.59%, 5.09%, 4.84%, 4.71%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、青色点缀、橙色点缀、冷暖平衡、深色背景、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、棕色点缀、青色点缀、冷暖平衡、深色背景、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、欢快、跳脱、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>900015</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>A Brush With Death</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>#9E6240, #BF7E54, #291A14, #AEA094, #734D39, #4C2F22, #C1BEBA, #8E7F71, #E1E4E3</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>17.47%, 14.71%, 12.41%, 12.23%, 10.66%, 10.07%, 8.21%, 7.68%, 6.56%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、温暖配色、中明度配色、柔和中饱和、复古大地色、红橙暖调、电影海报感</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>900016</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>A christmas carol wpa poster</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>#D2C09A, #CAB88E, #312D21, #121108, #463F2A, #B3A37C, #9C8D69, #827554, #665A3C</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>29.32%, 19.79%, 19.78%, 10.86%, 7.95%, 4.01%, 3.09%, 2.69%, 2.51%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、中明度配色、柔和中饱和、强对比、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、黑白深色、黑色系、温暖配色、中明度配色、柔和中饱和、强对比、电影海报感</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>900017</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>A fleeting encounter film poster</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>#050403, #837B5B, #9A9978, #381B08, #5C6150, #353832, #6E421C, #BAB797, #E9E1C0</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>29.97%, 12.18%, 11.82%, 10.47%, 8.50%, 8.31%, 8.20%, 7.28%, 3.26%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、深色背景、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、棕色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>900018</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>A Girl from Palestine poster</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>#C3C3C1, #E2E0DC, #A699AB, #837391, #D94D34, #C12C12, #554771, #1C154C, #751C1A</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>22.81%, 17.27%, 12.61%, 11.46%, 10.61%, 9.15%, 8.38%, 4.56%, 3.16%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、红色点缀、紫色点缀、冷暖平衡、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、鲜明红色、红色系、紫色点缀、冷暖平衡、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>欢快、跳脱、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>900019</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>A Kiss for Cinderella 1925</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>#F4F2E6, #DDB17A, #7E644A, #B1895D, #A3D6DE, #513E2C, #19110C, #DECDB3, #939E95</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>15.83%, 12.81%, 12.76%, 12.14%, 10.15%, 9.94%, 9.72%, 9.58%, 7.07%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>温暖、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>900020</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>A Lost Silent Film -- 1918 (54387617645)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>#DDE8EA, #AEBDC2, #CDD6D3, #7D3A3E, #916161, #D4C0A9, #85122B, #A5908A, #4F3F46</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>16.92%, 15.71%, 14.91%, 14.51%, 9.47%, 8.10%, 7.92%, 7.28%, 5.18%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>鲜明红色、红色系、高级灰、灰色系、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、棕色点缀、红色点缀、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>900022</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Aama (film poster)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>#424046, #1E2527, #D0D8E0, #6F6266, #8D8991, #A3B0C1, #5583B2, #335B96, #EBDC5F</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>19.97%, 18.11%, 12.10%, 9.77%, 9.74%, 9.64%, 8.45%, 7.96%, 4.26%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、冷色系、蓝色点缀、冷感配色、中明度配色、柔和中饱和、极简黑白灰、电影海报感</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、蓝色点缀、冷暖平衡、中明度配色、柔和中饱和、极简黑白灰、电影海报感</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>冷静、高级、克制、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>高级、克制、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>900023</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Aan Tamil-language film poster</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>#010206, #EDEFF0, #101526, #2A3242, #B2B6BD, #465162, #D0D2D6, #68717E, #8C939E</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>16.12%, 13.97%, 11.31%, 11.26%, 10.01%, 9.82%, 9.81%, 9.05%, 8.66%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷色系、冷感配色、中明度配色、柔和中饱和、强对比</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷感配色、中明度配色、柔和中饱和、强对比、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>冷静、理性、清爽、高级、克制、抓眼</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>冷静、高级、克制、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>900024</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Abenteuer Lerchenberg (Cover)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>#010103, #1D1D20, #C8CACA, #494742, #6F7371, #979D9A, #E8EDEC, #A57B34, #E3B25D</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>54.86%, 11.50%, 8.12%, 7.34%, 6.22%, 5.73%, 2.53%, 1.99%, 1.71%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、冷暖平衡、深色背景、柔和中饱和、复古大地色、极简黑白灰、电影海报感</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、深色背景、柔和中饱和、复古大地色、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、高级、克制、怀旧、抓眼</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、高级、克制、怀旧、抓眼</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>900025</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Abenteuer mit Fix und Fax – Das fliegende Geschenk</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>#EEE6E1, #78ABC1, #64A2BA, #56A152, #3F3D38, #5E6E65, #D61E1C, #9EA29B, #B7993E</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>24.13%, 21.98%, 18.61%, 7.58%, 7.16%, 6.82%, 5.62%, 4.86%, 3.23%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>冷感蓝色、蓝色系、绿色点缀、红色点缀、冷感配色、明亮浅色、柔和中饱和、蓝绿冷调、电影海报感</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>冷感蓝色、蓝色系、绿色点缀、红色点缀、冷感配色、明亮浅色、柔和中饱和、蓝绿冷调、电影海报感</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、冷静、理性、清爽、抓眼</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、冷静、理性、清爽、欢快</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>900026</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Above the Clouds (1948)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>#F3D6A1, #E2C392, #C9AE83, #17100B, #2D2419, #AC946F, #473B2A, #69573D, #8A7657</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>21.68%, 18.07%, 11.12%, 9.21%, 8.97%, 8.96%, 7.64%, 7.64%, 6.71%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、中明度配色、柔和中饱和、强对比、复古大地色、电影海报感、视觉冲击</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>暖色系、棕色点缀、温暖配色、中明度配色、柔和中饱和、强对比、复古大地色、电影海报感、视觉冲击</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>900027</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Abraham Lincoln's Clemency Movie Posters</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>#F4F1EC, #E4CFBD, #2B1724, #4B323F, #CBB098, #BC886A, #805948, #CF4A39, #857A8A</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>23.48%, 12.69%, 12.43%, 12.22%, 9.84%, 8.99%, 8.89%, 6.84%, 4.63%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>暖色系、红色点缀、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、棕色点缀、红色点缀、温暖配色、中明度配色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>温暖、梦幻、浪漫、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>温暖、梦幻、浪漫、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>900028</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ach, te spodnie!</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>#D9D3B1, #E0DCBB, #D4C89E, #7A8881, #596D71, #B6B9A3, #395060, #99A192, #1C2B3E</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>33.78%, 27.10%, 12.06%, 5.23%, 5.14%, 4.86%, 4.85%, 4.85%, 2.14%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、明亮浅色、低饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、怀旧</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>900029</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Affiche 90 La dernière harde The Last Herd FrEn</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>#4B493F, #636158, #58564C, #3C3B35, #2D2D28, #805639, #B57443, #DFDFDD, #A6A6A2</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>25.25%, 19.41%, 18.31%, 16.61%, 11.34%, 4.06%, 2.51%, 1.26%, 1.25%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、深色背景、低饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、深色背景、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、温暖、抓眼</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、温暖、抓眼</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>900031</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Affiche du film Cri de pierre</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>#93CEDC, #DBE6E3, #E79F56, #D97E39, #B8592F, #402E2A, #7B412F, #E3B48A, #82776C</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>40.82%, 11.40%, 11.14%, 9.48%, 8.21%, 6.86%, 5.91%, 3.69%, 2.49%</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>明亮橙色、橙色系、红色点缀、冷暖平衡、明亮浅色、柔和中饱和、红橙暖调、电影海报感</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>黄棕色点缀、棕色点缀、冷暖平衡、明亮浅色、柔和中饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、理性、清爽、热烈、怀旧</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、理性、清爽、欢快、跳脱</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>900032</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Affiche du film El Ghoula</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>#2A2A2A, #A4A3A3, #929290, #151514, #424240, #6E6E68, #F7F66C, #C4C279, #CBCAC8</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>21.28%, 17.74%, 17.39%, 14.91%, 10.49%, 6.27%, 6.25%, 2.86%, 2.81%</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、黄色点缀、冷暖平衡、中明度配色、低饱和、极简黑白灰</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、冷暖平衡、中明度配色、低饱和、极简黑白灰、电影海报感</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>克制、安静、高级、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>克制、安静、高级、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>900033</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Affiche du film Kahla Oua Beida</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>#833F40, #CC8787, #ECEBEA, #D0C5BA, #080605, #996968, #5A5754, #362C2A, #BFA29D</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>33.12%, 17.41%, 16.47%, 7.52%, 7.36%, 5.92%, 5.89%, 3.21%, 3.11%</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>鲜明红色、红色系、温暖配色、中明度配色、柔和中饱和、红橙暖调、电影海报感</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>900034</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Affiche du film L'Enfer a dix ans</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>#F2EFEF, #25100D, #681813, #D4A28A, #E2C9C0, #7F473C, #C56C55, #CC2417, #8C8080</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>23.73%, 16.59%, 12.09%, 10.03%, 9.96%, 8.58%, 8.27%, 6.26%, 4.49%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>鲜明红色、红色系、温暖配色、中明度配色、柔和中饱和、强对比、电影海报感、视觉冲击</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>暖色系、红色点缀、棕色点缀、温暖配色、中明度配色、柔和中饱和、强对比、电影海报感、视觉冲击</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>温暖、欢快、跳脱、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>900035</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Affiche du film Les portes du silence</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>#0D0F17, #25282E, #C83E31, #C5CAD5, #4B4345, #706A66, #E0E0E3, #9B8D86, #BCAFA5</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>37.45%, 14.70%, 12.74%, 8.32%, 7.90%, 5.46%, 4.84%, 4.49%, 4.10%</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、红色点缀、冷暖平衡、中明度配色、柔和中饱和、强对比、极简黑白灰、电影海报感</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、红色点缀、冷暖平衡、中明度配色、柔和中饱和、强对比</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>高级、克制、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>高级、克制、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>900037</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Affiche du film Nuit d'opéra cambodgien</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>#5B4E4E, #443B3F, #6F6362, #2C272D, #131117, #877C79, #B5ABA0, #F0E2BE, #D8B74F</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>20.36%, 19.03%, 16.32%, 16.29%, 11.73%, 8.82%, 3.33%, 3.25%, 0.88%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、暖色系、温暖配色、深色背景、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、黑白深色、黑色系、温暖配色、深色背景、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、温暖、梦幻</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、克制、安静、温暖、梦幻</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>900038</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Affiche L’Éducatrice 2025</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>#060505, #37361E, #241913, #5E4C29, #AF8F5B, #85693C, #CCD4D5, #B8B3A1, #797F76</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>35.64%, 18.09%, 11.04%, 9.85%, 7.60%, 7.14%, 4.43%, 3.34%, 2.86%</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、橙色点缀、温暖配色、深色背景、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>棕色调、棕色系、黑白深色、黑色系、温暖配色、深色背景、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>沉稳、厚重、温暖、高级、克制、抓眼</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>900039</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Affiche originale de Passez muscade (1941)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>#FCFCE5, #181212, #46332A, #FAEF95, #A88265, #E6B074, #A3211E, #CBC3B0, #685D59</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>57.49%, 10.74%, 5.12%, 5.04%, 4.99%, 4.54%, 4.28%, 4.24%, 3.54%</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、明亮浅色、低饱和、极简黑白灰、电影海报感</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、温暖配色、明亮浅色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、高级</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>900040</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AFICHE LA BESTIA DEBE MORIR (1952)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>#DC4D45, #2F2822, #F1C49D, #7A6354, #F3E0D0, #554439, #958777, #C0AB98, #EA7E73</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>17.08%, 14.32%, 12.21%, 10.53%, 10.13%, 9.48%, 9.22%, 8.62%, 8.43%</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>鲜明红色、红色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>暖色系、红色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>温暖、热烈、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>900041</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Afiche Salvar el Amor</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>#1A1417, #3A3036, #816D68, #5B4E53, #AF8975, #D6BBA7, #8C5337, #EBE8E4, #E7AF63</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>33.10%, 17.58%, 10.62%, 9.89%, 9.27%, 8.02%, 4.37%, 4.09%, 3.07%</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、橙色点缀、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>黑白深色、黑色系、暖色系、温暖配色、中明度配色、柔和中饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>温暖、梦幻、浪漫、怀旧、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>温暖、梦幻、浪漫、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>900044</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ALEXANDER NOT SO GREAT (2013) by Alvin Soprano</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>#F8F0ED, #F0D6CB, #71493D, #DFB0A3, #986456, #C2867B, #462E2A, #080709, #67B6B5</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>36.31%, 16.11%, 10.29%, 9.20%, 8.87%, 7.44%, 7.03%, 3.93%, 0.81%</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>暖色系、温暖配色、明亮浅色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>米色浅色、米色系、棕色点缀、温暖配色、明亮浅色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>明亮、轻盈、克制、安静、温暖、抓眼</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>900045</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Alexander poster</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>#D1D1D1, #102940, #163650, #C4C5C6, #576673, #7A838A, #9EA4A8, #344C60, #EBEEED</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>33.02%, 26.50%, 10.71%, 7.99%, 5.44%, 5.40%, 5.03%, 4.75%, 1.16%</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、冷色系、蓝色点缀、冷感配色、中明度配色、柔和中饱和、强对比、电影海报感</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、蓝色点缀、冷感配色、中明度配色、柔和中饱和、强对比、电影海报感、视觉冲击</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>冷静、理性、清爽、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>冷静、理性、清爽、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>900046</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Alf's Carpet 1929 poster</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>#EBE4DB, #CA795D, #383431, #514A46, #D5CEC3, #696663, #928F88, #BCACA0, #915A47</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>25.03%, 18.03%, 11.11%, 10.20%, 10.13%, 8.79%, 6.99%, 6.70%, 3.01%</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>暖色系、橙色点缀、温暖配色、中明度配色、低饱和、复古大地色、电影海报感</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、温暖配色、中明度配色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>克制、安静、温暖、高级、抓眼、宣传感</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-06-06 18:17:32</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>900048</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>All These Creatures Poster</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Movie Poster</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>电影海报、平面设计、视觉传达</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>#33393D, #3D4C5B, #717C85, #8B9096, #576572, #A6A8AC, #1A222B, #585648, #DAD6D2</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>15.24%, 14.81%, 13.53%, 13.46%, 13.10%, 9.20%, 8.15%, 7.50%, 5.01%</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>冷色系、冷感配色、中明度配色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>高级灰、灰色系、冷感配色、中明度配色、低饱和、电影海报感</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>克制、安静、冷静、理性、清爽、抓眼</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>克制、安静、冷静、理性、清爽、抓眼</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>以用户检索需求为目标，根据9色HEX、颜色比例、色系、整体色调和风格分类生成更贴近原图的色彩/情绪标签</t>
         </is>
       </c>
     </row>
